--- a/Team-Data/2011-12/2-13-2011-12.xlsx
+++ b/Team-Data/2011-12/2-13-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>3.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
         <v>6</v>
@@ -757,7 +824,7 @@
         <v>12</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK2" t="n">
         <v>12</v>
@@ -775,13 +842,13 @@
         <v>20</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>23</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
         <v>12</v>
@@ -793,7 +860,7 @@
         <v>5</v>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -942,7 +1009,7 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL3" t="n">
         <v>18</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>28</v>
@@ -978,7 +1045,7 @@
         <v>22</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -1025,61 +1092,61 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.107</v>
+        <v>0.111</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.4</v>
+        <v>33.6</v>
       </c>
       <c r="J4" t="n">
-        <v>80.7</v>
+        <v>81</v>
       </c>
       <c r="K4" t="n">
         <v>0.414</v>
       </c>
       <c r="L4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.297</v>
+        <v>0.292</v>
       </c>
       <c r="O4" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="Q4" t="n">
         <v>0.736</v>
       </c>
       <c r="R4" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="S4" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U4" t="n">
         <v>19.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W4" t="n">
         <v>5.7</v>
@@ -1094,16 +1161,16 @@
         <v>19.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.4</v>
+        <v>19.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>86.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14.4</v>
+        <v>-14.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
@@ -1115,13 +1182,13 @@
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1133,22 +1200,22 @@
         <v>26</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>23</v>
       </c>
       <c r="AP4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>21</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>22</v>
-      </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1157,13 +1224,13 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY4" t="n">
         <v>26</v>
@@ -1172,7 +1239,7 @@
         <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK5" t="n">
         <v>5</v>
@@ -1336,16 +1403,16 @@
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW5" t="n">
         <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
         <v>9</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1534,28 @@
         <v>-3.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF6" t="n">
         <v>23</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>23</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI6" t="n">
         <v>19</v>
       </c>
       <c r="AJ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL6" t="n">
         <v>13</v>
@@ -1512,10 +1579,10 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
         <v>18</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.621</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
@@ -1589,7 +1656,7 @@
         <v>35.9</v>
       </c>
       <c r="J7" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K7" t="n">
         <v>0.442</v>
@@ -1598,40 +1665,40 @@
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="N7" t="n">
         <v>0.326</v>
       </c>
       <c r="O7" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P7" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.737</v>
+        <v>0.738</v>
       </c>
       <c r="R7" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="S7" t="n">
-        <v>32.9</v>
+        <v>33.1</v>
       </c>
       <c r="T7" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="U7" t="n">
         <v>21.5</v>
       </c>
       <c r="V7" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Y7" t="n">
         <v>4.4</v>
@@ -1640,7 +1707,7 @@
         <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AB7" t="n">
         <v>94.7</v>
@@ -1649,10 +1716,10 @@
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,13 +1728,13 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK7" t="n">
         <v>16</v>
@@ -1679,31 +1746,31 @@
         <v>5</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>4</v>
@@ -1718,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1846,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -1876,7 +1943,7 @@
         <v>29</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2095,7 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ9" t="n">
         <v>26</v>
@@ -2049,13 +2116,13 @@
         <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ9" t="n">
         <v>6</v>
       </c>
       <c r="AR9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>29</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" t="n">
         <v>14</v>
       </c>
       <c r="G10" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,64 +2202,64 @@
         <v>38</v>
       </c>
       <c r="J10" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.465</v>
       </c>
       <c r="L10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.396</v>
       </c>
       <c r="O10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
         <v>20.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.738</v>
+        <v>0.735</v>
       </c>
       <c r="R10" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="S10" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T10" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U10" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="V10" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
         <v>5.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z10" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>17.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="AD10" t="n">
         <v>30</v>
@@ -2204,16 +2271,16 @@
         <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
         <v>11</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK10" t="n">
         <v>4</v>
@@ -2228,16 +2295,16 @@
         <v>1</v>
       </c>
       <c r="AO10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR10" t="n">
         <v>26</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>24</v>
       </c>
       <c r="AS10" t="n">
         <v>24</v>
@@ -2246,7 +2313,7 @@
         <v>27</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
         <v>13</v>
@@ -2258,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ10" t="n">
         <v>29</v>
@@ -2270,7 +2337,7 @@
         <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>11</v>
@@ -2392,7 +2459,7 @@
         <v>6</v>
       </c>
       <c r="AI11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -2407,7 +2474,7 @@
         <v>10</v>
       </c>
       <c r="AN11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO11" t="n">
         <v>28</v>
@@ -2416,10 +2483,10 @@
         <v>29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
@@ -2431,13 +2498,13 @@
         <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW11" t="n">
         <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY11" t="n">
         <v>13</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
         <v>7</v>
@@ -2574,13 +2641,13 @@
         <v>17</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>23</v>
@@ -2613,7 +2680,7 @@
         <v>27</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2663,34 +2730,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E13" t="n">
         <v>17</v>
       </c>
       <c r="F13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.654</v>
+        <v>0.68</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J13" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K13" t="n">
         <v>0.46</v>
       </c>
       <c r="L13" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M13" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="N13" t="n">
         <v>0.356</v>
@@ -2702,55 +2769,55 @@
         <v>25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.676</v>
+        <v>0.678</v>
       </c>
       <c r="R13" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S13" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="T13" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="U13" t="n">
         <v>22</v>
       </c>
       <c r="V13" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="W13" t="n">
         <v>8</v>
       </c>
       <c r="X13" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z13" t="n">
         <v>21.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.40000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>4</v>
       </c>
       <c r="AG13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2759,7 +2826,7 @@
         <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK13" t="n">
         <v>7</v>
@@ -2786,16 +2853,16 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AT13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
         <v>12</v>
@@ -2804,10 +2871,10 @@
         <v>11</v>
       </c>
       <c r="AY13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>11</v>
@@ -2965,10 +3032,10 @@
         <v>15</v>
       </c>
       <c r="AR14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>0.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3117,7 +3184,7 @@
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>15</v>
@@ -3150,22 +3217,22 @@
         <v>4</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU15" t="n">
         <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>25</v>
@@ -3180,7 +3247,7 @@
         <v>22</v>
       </c>
       <c r="BC15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3209,28 +3276,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>0.759</v>
+        <v>0.75</v>
       </c>
       <c r="H16" t="n">
         <v>48.9</v>
       </c>
       <c r="I16" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J16" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.485</v>
+        <v>0.483</v>
       </c>
       <c r="L16" t="n">
         <v>5.7</v>
@@ -3239,25 +3306,25 @@
         <v>14.6</v>
       </c>
       <c r="N16" t="n">
-        <v>0.392</v>
+        <v>0.388</v>
       </c>
       <c r="O16" t="n">
         <v>20.9</v>
       </c>
       <c r="P16" t="n">
-        <v>26.9</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="R16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="S16" t="n">
         <v>32.9</v>
       </c>
       <c r="T16" t="n">
-        <v>42.7</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
         <v>20.9</v>
@@ -3269,7 +3336,7 @@
         <v>8.6</v>
       </c>
       <c r="X16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
         <v>4.2</v>
@@ -3281,13 +3348,13 @@
         <v>22</v>
       </c>
       <c r="AB16" t="n">
-        <v>103.4</v>
+        <v>103</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -3305,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3317,7 +3384,7 @@
         <v>24</v>
       </c>
       <c r="AN16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO16" t="n">
         <v>3</v>
@@ -3347,10 +3414,10 @@
         <v>7</v>
       </c>
       <c r="AX16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
         <v>19</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3391,148 +3458,148 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
         <v>84</v>
       </c>
       <c r="K17" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.336</v>
+        <v>0.334</v>
       </c>
       <c r="O17" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P17" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.788</v>
+        <v>0.786</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.6</v>
       </c>
       <c r="T17" t="n">
-        <v>41.4</v>
+        <v>41.6</v>
       </c>
       <c r="U17" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="V17" t="n">
         <v>14.5</v>
       </c>
       <c r="W17" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X17" t="n">
         <v>5.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>20</v>
       </c>
       <c r="AF17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG17" t="n">
         <v>20</v>
       </c>
-      <c r="AG17" t="n">
-        <v>21</v>
-      </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ17" t="n">
         <v>2</v>
       </c>
       <c r="AK17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AM17" t="n">
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO17" t="n">
         <v>16</v>
       </c>
       <c r="AP17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS17" t="n">
         <v>28</v>
       </c>
       <c r="AT17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>8</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
@@ -3544,7 +3611,7 @@
         <v>15</v>
       </c>
       <c r="BC17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0.448</v>
+        <v>0.464</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3594,7 +3661,7 @@
         <v>80.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L18" t="n">
         <v>6.5</v>
@@ -3603,76 +3670,76 @@
         <v>20</v>
       </c>
       <c r="N18" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="O18" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="P18" t="n">
         <v>26.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.771</v>
       </c>
       <c r="R18" t="n">
         <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T18" t="n">
-        <v>44.7</v>
+        <v>44.5</v>
       </c>
       <c r="U18" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="V18" t="n">
         <v>16.4</v>
       </c>
       <c r="W18" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>18</v>
       </c>
       <c r="AF18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH18" t="n">
         <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
         <v>15</v>
@@ -3681,7 +3748,7 @@
         <v>11</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>4</v>
@@ -3690,13 +3757,13 @@
         <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS18" t="n">
         <v>7</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>6</v>
       </c>
       <c r="AT18" t="n">
         <v>3</v>
@@ -3708,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="AW18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>11</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3848,10 +3915,10 @@
         <v>26</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -3937,67 +4004,67 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.179</v>
+        <v>0.148</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
       </c>
       <c r="I20" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J20" t="n">
-        <v>77.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.44</v>
       </c>
       <c r="L20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
         <v>12.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.292</v>
+        <v>0.293</v>
       </c>
       <c r="O20" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="R20" t="n">
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V20" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y20" t="n">
         <v>5.5</v>
@@ -4006,16 +4073,16 @@
         <v>20.6</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="AB20" t="n">
         <v>87.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-5.8</v>
+        <v>-6.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE20" t="n">
         <v>29</v>
@@ -4027,7 +4094,7 @@
         <v>29</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4045,22 +4112,22 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR20" t="n">
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
         <v>24</v>
@@ -4075,7 +4142,7 @@
         <v>21</v>
       </c>
       <c r="AX20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY20" t="n">
         <v>22</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>0.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4212,13 +4279,13 @@
         <v>14</v>
       </c>
       <c r="AI21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK21" t="n">
         <v>21</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>10</v>
@@ -4257,7 +4324,7 @@
         <v>2</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY21" t="n">
         <v>13</v>
@@ -4272,7 +4339,7 @@
         <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>1</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4421,13 +4488,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>28</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -4483,34 +4550,34 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.621</v>
+        <v>0.607</v>
       </c>
       <c r="H23" t="n">
         <v>48.5</v>
       </c>
       <c r="I23" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="J23" t="n">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K23" t="n">
         <v>0.433</v>
       </c>
       <c r="L23" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M23" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="N23" t="n">
         <v>0.387</v>
@@ -4519,16 +4586,16 @@
         <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.656</v>
+        <v>0.651</v>
       </c>
       <c r="R23" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S23" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T23" t="n">
         <v>43.1</v>
@@ -4537,13 +4604,13 @@
         <v>19.9</v>
       </c>
       <c r="V23" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="W23" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y23" t="n">
         <v>4.4</v>
@@ -4552,19 +4619,19 @@
         <v>18.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>93.2</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF23" t="n">
         <v>9</v>
@@ -4573,10 +4640,10 @@
         <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AJ23" t="n">
         <v>29</v>
@@ -4609,22 +4676,22 @@
         <v>8</v>
       </c>
       <c r="AT23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX23" t="n">
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ23" t="n">
         <v>5</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -4665,97 +4732,97 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="H24" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I24" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J24" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L24" t="n">
         <v>6.1</v>
       </c>
       <c r="M24" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="P24" t="n">
-        <v>19.4</v>
+        <v>19.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.722</v>
+        <v>0.717</v>
       </c>
       <c r="R24" t="n">
         <v>9.6</v>
       </c>
       <c r="S24" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T24" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U24" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="W24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X24" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y24" t="n">
         <v>4.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="AA24" t="n">
         <v>17.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>95.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AC24" t="n">
         <v>9.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>4</v>
       </c>
       <c r="AF24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI24" t="n">
         <v>5</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL24" t="n">
         <v>17</v>
@@ -4773,7 +4840,7 @@
         <v>20</v>
       </c>
       <c r="AN24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,19 +4855,19 @@
         <v>28</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV24" t="n">
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>22</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.429</v>
+        <v>0.444</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J25" t="n">
         <v>80.8</v>
@@ -4871,13 +4938,13 @@
         <v>0.448</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M25" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.344</v>
+        <v>0.351</v>
       </c>
       <c r="O25" t="n">
         <v>14.2</v>
@@ -4889,7 +4956,7 @@
         <v>0.771</v>
       </c>
       <c r="R25" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S25" t="n">
         <v>31</v>
@@ -4898,13 +4965,13 @@
         <v>41</v>
       </c>
       <c r="U25" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="V25" t="n">
         <v>14.5</v>
       </c>
       <c r="W25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X25" t="n">
         <v>5.2</v>
@@ -4916,46 +4983,46 @@
         <v>18.6</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AE25" t="n">
         <v>20</v>
       </c>
       <c r="AF25" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG25" t="n">
         <v>20</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>21</v>
       </c>
       <c r="AH25" t="n">
         <v>28</v>
       </c>
       <c r="AI25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ25" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AK25" t="n">
         <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AM25" t="n">
         <v>13</v>
       </c>
       <c r="AN25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
         <v>29</v>
@@ -4964,10 +5031,10 @@
         <v>30</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4976,7 +5043,7 @@
         <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
         <v>9</v>
@@ -4994,7 +5061,7 @@
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB25" t="n">
         <v>19</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>5.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
         <v>14</v>
       </c>
       <c r="AF26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
@@ -5158,7 +5225,7 @@
         <v>13</v>
       </c>
       <c r="AU26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
@@ -5176,7 +5243,7 @@
         <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
@@ -5328,13 +5395,13 @@
         <v>8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>4.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" t="n">
         <v>5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>4</v>
       </c>
       <c r="AG28" t="n">
         <v>5</v>
@@ -5507,13 +5574,13 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ28" t="n">
         <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS28" t="n">
         <v>11</v>
@@ -5522,7 +5589,7 @@
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5732,7 @@
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI29" t="n">
         <v>30</v>
@@ -5683,7 +5750,7 @@
         <v>18</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>17</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" t="n">
-        <v>0.519</v>
+        <v>0.538</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.453</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
         <v>3.8</v>
@@ -5790,28 +5857,28 @@
         <v>0.297</v>
       </c>
       <c r="O30" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P30" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.74</v>
+        <v>0.741</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U30" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V30" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W30" t="n">
         <v>7.9</v>
@@ -5826,25 +5893,25 @@
         <v>22.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>96</v>
+        <v>96.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
       </c>
       <c r="AF30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG30" t="n">
         <v>15</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>16</v>
       </c>
       <c r="AH30" t="n">
         <v>5</v>
@@ -5853,7 +5920,7 @@
         <v>10</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK30" t="n">
         <v>10</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO30" t="n">
         <v>7</v>
@@ -5877,13 +5944,13 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AS30" t="n">
         <v>18</v>
       </c>
       <c r="AT30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>14</v>
@@ -5904,7 +5971,7 @@
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-9.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,7 +6096,7 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>18</v>
@@ -6053,16 +6120,16 @@
         <v>21</v>
       </c>
       <c r="AP31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ31" t="n">
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
         <v>21</v>
@@ -6083,7 +6150,7 @@
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-13-2011-12</t>
+          <t>2012-02-13</t>
         </is>
       </c>
     </row>
